--- a/test/fixtures/duplicate-sheets.xlsx
+++ b/test/fixtures/duplicate-sheets.xlsx
@@ -428,6 +428,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -442,6 +443,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -456,6 +458,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -495,6 +498,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -509,6 +513,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -523,6 +528,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -562,6 +568,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -576,6 +583,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -590,6 +598,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -629,6 +638,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,6 +653,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -657,6 +668,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
